--- a/result/morris/morris_first_inf_ONLY_MAE_N512_seed123.xlsx
+++ b/result/morris/morris_first_inf_ONLY_MAE_N512_seed123.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,65 +453,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dispersal__rain_min</t>
+          <t>zoospore_alive__vpd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.6404079861111</v>
+        <v>-8.028591579861114</v>
       </c>
       <c r="C2" t="n">
-        <v>18.90006510416665</v>
+        <v>18.0303276909722</v>
       </c>
       <c r="D2" t="n">
-        <v>30.59678341161888</v>
+        <v>27.67022067929215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zoospore_alive__vpd</t>
+          <t>dispersal__rain_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-11.39436848958333</v>
+        <v>2.187554253472223</v>
       </c>
       <c r="C3" t="n">
-        <v>17.66270616319444</v>
+        <v>15.51101345486111</v>
       </c>
       <c r="D3" t="n">
-        <v>29.92554389137441</v>
+        <v>25.42228049181002</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>infection__infection_condition</t>
+          <t>thresholds__min_spores</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.00748697916666</v>
+        <v>3.332736545138891</v>
       </c>
       <c r="C4" t="n">
-        <v>17.55891927083334</v>
+        <v>14.02338324652777</v>
       </c>
       <c r="D4" t="n">
-        <v>25.39786980940193</v>
+        <v>22.56495857584704</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mp_tmp__rh_wet_night</t>
+          <t>infection__infection_condition</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.49983723958333</v>
+        <v>5.999674479166668</v>
       </c>
       <c r="C5" t="n">
-        <v>15.74994574652777</v>
+        <v>13.35405815972223</v>
       </c>
       <c r="D5" t="n">
-        <v>21.1142980258962</v>
+        <v>22.17367992429256</v>
       </c>
     </row>
     <row r="6">
@@ -521,125 +521,141 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.02886284722222254</v>
+        <v>0.8207465277777776</v>
       </c>
       <c r="C6" t="n">
-        <v>6.12033420138889</v>
+        <v>8.685763888888895</v>
       </c>
       <c r="D6" t="n">
-        <v>14.35177252728647</v>
+        <v>17.94993842405459</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sporulation__MP_min</t>
+          <t>mp_tmp__rh_wet_night</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.356391059027778</v>
+        <v>1.76931423611111</v>
       </c>
       <c r="C7" t="n">
-        <v>3.40814887152778</v>
+        <v>7.901475694444445</v>
       </c>
       <c r="D7" t="n">
-        <v>7.81339519447056</v>
+        <v>13.92165055727116</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dispersal__wind_min</t>
+          <t>sporulation__Topt</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7396375868055557</v>
+        <v>-0.610785590277778</v>
       </c>
       <c r="C8" t="n">
-        <v>2.498101128472223</v>
+        <v>4.362196180555557</v>
       </c>
       <c r="D8" t="n">
-        <v>9.199418299618864</v>
+        <v>12.83897078619885</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sporulation__Topt</t>
+          <t>dispersal__wind_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5453016493055557</v>
+        <v>2.420898437500001</v>
       </c>
       <c r="C9" t="n">
-        <v>2.478461371527778</v>
+        <v>4.137586805555559</v>
       </c>
       <c r="D9" t="n">
-        <v>10.6408387192408</v>
+        <v>9.414515055161278</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>deposition__rain_min</t>
+          <t>sporulation__Tmin</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.550618489583333</v>
+        <v>-1.038791232638889</v>
       </c>
       <c r="C10" t="n">
-        <v>1.828179253472223</v>
+        <v>3.075466579861112</v>
       </c>
       <c r="D10" t="n">
-        <v>6.727343648171867</v>
+        <v>11.33986024117148</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>incubation__spl_end</t>
+          <t>zoospore_alive__rain</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7347547743055556</v>
+        <v>0.6042209201388887</v>
       </c>
       <c r="C11" t="n">
-        <v>1.226182725694444</v>
+        <v>2.03835720486111</v>
       </c>
       <c r="D11" t="n">
-        <v>1.253283708030523</v>
+        <v>7.951751647965789</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>zoospore_alive__rain</t>
+          <t>deposition__rain_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1542426215277777</v>
+        <v>0.6150173611111109</v>
       </c>
       <c r="C12" t="n">
-        <v>1.09033203125</v>
+        <v>1.396484375</v>
       </c>
       <c r="D12" t="n">
-        <v>5.68201003156966</v>
+        <v>5.491123687484022</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sporulation__Tmin</t>
+          <t>sporulation__MP_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4239908854166667</v>
+        <v>-0.1247829861111111</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8669162326388887</v>
+        <v>1.379991319444444</v>
       </c>
       <c r="D13" t="n">
-        <v>5.513065854543776</v>
+        <v>4.483856086477293</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>incubation__spl_end</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3431532118055555</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.093261718749999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.337532240678247</v>
       </c>
     </row>
   </sheetData>
